--- a/Project/outputs/tables/table_spillover_calm.xlsx
+++ b/Project/outputs/tables/table_spillover_calm.xlsx
@@ -436,19 +436,19 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>CAC40</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DAX</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Nikkei</t>
@@ -456,17 +456,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>HangSeng</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CSI300</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -482,133 +482,133 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.39</v>
+        <v>43.89</v>
       </c>
       <c r="C2" t="n">
-        <v>15.01</v>
+        <v>13.43</v>
       </c>
       <c r="D2" t="n">
-        <v>13.56</v>
+        <v>14.83</v>
       </c>
       <c r="E2" t="n">
-        <v>11.38</v>
+        <v>14.88</v>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>3.85</v>
       </c>
       <c r="G2" t="n">
-        <v>1.97</v>
+        <v>5.83</v>
       </c>
       <c r="H2" t="n">
-        <v>0.63</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>22.52</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>9.380000000000001</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.93</v>
+        <v>11.58</v>
       </c>
       <c r="C3" t="n">
-        <v>25.22</v>
+        <v>31.97</v>
       </c>
       <c r="D3" t="n">
-        <v>21.21</v>
+        <v>24.53</v>
       </c>
       <c r="E3" t="n">
-        <v>19.88</v>
+        <v>18.09</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="G3" t="n">
-        <v>4.11</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.33</v>
+        <v>4.65</v>
       </c>
       <c r="I3" t="n">
-        <v>10.22</v>
+        <v>0.61</v>
       </c>
       <c r="J3" t="n">
-        <v>11.28</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>12.21</v>
       </c>
       <c r="C4" t="n">
-        <v>23.09</v>
+        <v>23.64</v>
       </c>
       <c r="D4" t="n">
-        <v>26.88</v>
+        <v>31.19</v>
       </c>
       <c r="E4" t="n">
-        <v>17.55</v>
+        <v>21.61</v>
       </c>
       <c r="F4" t="n">
-        <v>2.63</v>
+        <v>3.71</v>
       </c>
       <c r="G4" t="n">
-        <v>3.96</v>
+        <v>3.19</v>
       </c>
       <c r="H4" t="n">
-        <v>2.16</v>
+        <v>3.73</v>
       </c>
       <c r="I4" t="n">
-        <v>11.72</v>
+        <v>0.72</v>
       </c>
       <c r="J4" t="n">
-        <v>10.04</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.3</v>
+        <v>13.16</v>
       </c>
       <c r="C5" t="n">
-        <v>19.6</v>
+        <v>18.09</v>
       </c>
       <c r="D5" t="n">
-        <v>15.2</v>
+        <v>22.84</v>
       </c>
       <c r="E5" t="n">
-        <v>27.24</v>
+        <v>34.79</v>
       </c>
       <c r="F5" t="n">
-        <v>6.48</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.539999999999999</v>
+        <v>3.53</v>
       </c>
       <c r="H5" t="n">
-        <v>3.17</v>
+        <v>3.34</v>
       </c>
       <c r="I5" t="n">
-        <v>8.460000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="J5" t="n">
-        <v>11.42</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -618,133 +618,133 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.34</v>
+        <v>8.58</v>
       </c>
       <c r="C6" t="n">
-        <v>10.61</v>
+        <v>7.73</v>
       </c>
       <c r="D6" t="n">
-        <v>9.35</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>13.85</v>
+        <v>6.81</v>
       </c>
       <c r="F6" t="n">
-        <v>33.44</v>
+        <v>50.14</v>
       </c>
       <c r="G6" t="n">
-        <v>15.03</v>
+        <v>8.16</v>
       </c>
       <c r="H6" t="n">
-        <v>4.15</v>
+        <v>9.58</v>
       </c>
       <c r="I6" t="n">
-        <v>5.23</v>
+        <v>1.01</v>
       </c>
       <c r="J6" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.99</v>
+        <v>9.34</v>
       </c>
       <c r="C7" t="n">
-        <v>6.27</v>
+        <v>8.77</v>
       </c>
       <c r="D7" t="n">
-        <v>5.55</v>
+        <v>8.31</v>
       </c>
       <c r="E7" t="n">
-        <v>14.4</v>
+        <v>7.2</v>
       </c>
       <c r="F7" t="n">
-        <v>11.45</v>
+        <v>7.4</v>
       </c>
       <c r="G7" t="n">
-        <v>40.31</v>
+        <v>44.62</v>
       </c>
       <c r="H7" t="n">
-        <v>10.15</v>
+        <v>13.71</v>
       </c>
       <c r="I7" t="n">
-        <v>5.87</v>
+        <v>0.65</v>
       </c>
       <c r="J7" t="n">
-        <v>6.68</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.74</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1.59</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1.39</v>
+        <v>8.49</v>
       </c>
       <c r="E8" t="n">
-        <v>5.04</v>
+        <v>7.86</v>
       </c>
       <c r="F8" t="n">
-        <v>3.23</v>
+        <v>8.02</v>
       </c>
       <c r="G8" t="n">
-        <v>16.89</v>
+        <v>12.97</v>
       </c>
       <c r="H8" t="n">
-        <v>69.13</v>
+        <v>39.58</v>
       </c>
       <c r="I8" t="n">
-        <v>0.98</v>
+        <v>5.16</v>
       </c>
       <c r="J8" t="n">
-        <v>2.91</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.71</v>
+        <v>0.78</v>
       </c>
       <c r="C9" t="n">
-        <v>14.08</v>
+        <v>1.72</v>
       </c>
       <c r="D9" t="n">
-        <v>14.01</v>
+        <v>1.26</v>
       </c>
       <c r="E9" t="n">
-        <v>9.289999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.18</v>
+        <v>0.68</v>
       </c>
       <c r="G9" t="n">
-        <v>2.94</v>
+        <v>0.33</v>
       </c>
       <c r="H9" t="n">
-        <v>0.71</v>
+        <v>10.15</v>
       </c>
       <c r="I9" t="n">
-        <v>35.08</v>
+        <v>84.39</v>
       </c>
       <c r="J9" t="n">
-        <v>8.130000000000001</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.33</v>
+        <v>7.01</v>
       </c>
       <c r="C10" t="n">
-        <v>9.35</v>
+        <v>8.5</v>
       </c>
       <c r="D10" t="n">
-        <v>9.140000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="E10" t="n">
-        <v>9.09</v>
+        <v>8.15</v>
       </c>
       <c r="F10" t="n">
-        <v>8.32</v>
+        <v>6.23</v>
       </c>
       <c r="G10" t="n">
-        <v>7.46</v>
+        <v>6.92</v>
       </c>
       <c r="H10" t="n">
-        <v>3.86</v>
+        <v>7.55</v>
       </c>
       <c r="I10" t="n">
-        <v>8.119999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="J10" t="n">
-        <v>63.66</v>
+        <v>54.93</v>
       </c>
     </row>
   </sheetData>
